--- a/KAMCHATKA_ZAPOLNENIE/09_ООО_БК-Арматура.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/09_ООО_БК-Арматура.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,293 +632,222 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>1.3/93</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ГОСТ 5762-2002</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>полнопроходной</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>до +225°С</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Вода,пар</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>серый чугун СЧ</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>У2, УХЛ4</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>фланец-фланец</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Ручное</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>маховик</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>любое</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Материал крышки ,диски,маховик,клин-серый чугун,Шпиндель — Ст 45 ГОСТ 1412</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>длина — 180мм</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.3/95</t>
+          <t>1.3/93</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
+          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ 5762-2002,  Гермитичность ГОСТ 9544-2015</t>
+          <t>ГОСТ 5762-2002</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -978,12 +907,12 @@
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Длина — 230мм</t>
+          <t>длина — 180мм</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -1007,31 +936,31 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.6/47</t>
+          <t>1.3/95</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
+          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ТУ УЗ 22-03326877-021-96</t>
+          <t>ГОСТ 5762-2002,  Гермитичность ГОСТ 9544-2015</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>полнопроходной</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1041,64 +970,57 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>до +225</t>
+          <t>до +225°С</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>вода, пар</t>
+          <t>Вода,пар</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>серый чугун СЧ 18 (СЧ 20)</t>
+          <t>серый чугун СЧ</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>У</t>
+          <t>У2, УХЛ4</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>фланцевый</t>
+          <t>фланец-фланец</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>ручной (маховик)</t>
+          <t>Ручное</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>маховик</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>любое, кроме маховиком вниз</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Шпиндель — сталь 20Х13;
-Кольцо уплотнительное, втулка резьбовая — латунь ЛЦ38МцС2;
-Прокладка под крышку — паронит ПОН;
-Набивка уплотнительная — АП-31;</t>
+          <t>Материал крышки ,диски,маховик,клин-серый чугун,Шпиндель — Ст 45 ГОСТ 1412</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Длина — 230мм</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -1122,16 +1044,16 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.6/49</t>
+          <t>1.6/47</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
+          <t>Задвижка 30ч6бр Ду 50 Ру 10</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1141,7 +1063,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1213,7 +1135,7 @@
         </is>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1236,44 +1158,159 @@
       <c r="AE8" s="7" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="10" t="inlineStr"/>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="10" t="inlineStr"/>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="10" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr"/>
-      <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr"/>
-      <c r="T9" s="10" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr"/>
-      <c r="V9" s="10" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr"/>
-      <c r="X9" s="10" t="inlineStr"/>
-      <c r="Y9" s="10" t="inlineStr"/>
-      <c r="Z9" s="10" t="inlineStr"/>
-      <c r="AA9" s="10" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>1.6/49</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Задвижка 30ч6бр Ду 100 Ру 10</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ТУ УЗ 22-03326877-021-96</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>до +225</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>вода, пар</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>серый чугун СЧ 18 (СЧ 20)</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>ручной (маховик)</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>любое, кроме маховиком вниз</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Шпиндель — сталь 20Х13;
+Кольцо уплотнительное, втулка резьбовая — латунь ЛЦ38МцС2;
+Прокладка под крышку — паронит ПОН;
+Набивка уплотнительная — АП-31;</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="n"/>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="7" t="n"/>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n"/>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="9">
+        <f>AA9*S9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="7" t="n"/>
+      <c r="AD9" s="7" t="n"/>
+      <c r="AE9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr"/>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr"/>
+      <c r="P10" s="10" t="inlineStr"/>
+      <c r="Q10" s="10" t="inlineStr"/>
+      <c r="R10" s="10" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr"/>
+      <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr"/>
+      <c r="V10" s="10" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr"/>
+      <c r="X10" s="10" t="inlineStr"/>
+      <c r="Y10" s="10" t="inlineStr"/>
+      <c r="Z10" s="10" t="inlineStr"/>
+      <c r="AA10" s="10" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB9" s="11">
-        <f>SUM(AB5:AB8)</f>
+      <c r="AB10" s="11">
+        <f>SUM(AB6:AB9)</f>
         <v/>
       </c>
-      <c r="AC9" s="2" t="n"/>
-      <c r="AD9" s="2" t="n"/>
-      <c r="AE9" s="2" t="n"/>
+      <c r="AC10" s="2" t="n"/>
+      <c r="AD10" s="2" t="n"/>
+      <c r="AE10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
